--- a/merged_breast_cancer_data.xlsx
+++ b/merged_breast_cancer_data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\CANCER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Documents\GitHub\NRF\NRF_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EA2499-A3E3-42E7-A8AB-F7A12EE6F061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18996" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18996" uniqueCount="853">
   <si>
     <t>age</t>
   </si>
@@ -2576,12 +2575,15 @@
   </si>
   <si>
     <t>breast biopsy : diffuse non-hodgkin's lymphoma</t>
+  </si>
+  <si>
+    <t>findings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2937,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X1055"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3013,7 +3015,7 @@
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>90</v>
+        <v>852</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>22</v>
